--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_25-07-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff683f0e935+77845]
-	GetHandleVerifier [0x0x7ff683f0e990+77936]
-	(No symbol) [0x0x7ff683cc9cda]
-	(No symbol) [0x0x7ff683d206aa]
-	(No symbol) [0x0x7ff683d2095c]
-	(No symbol) [0x0x7ff683d73d07]
-	(No symbol) [0x0x7ff683d4890f]
-	(No symbol) [0x0x7ff683d70b07]
-	(No symbol) [0x0x7ff683d486a3]
-	(No symbol) [0x0x7ff683d11791]
-	(No symbol) [0x0x7ff683d12523]
-	GetHandleVerifier [0x0x7ff6841e684d+3059501]
-	GetHandleVerifier [0x0x7ff6841e0c0d+3035885]
-	GetHandleVerifier [0x0x7ff684200400+3164896]
-	GetHandleVerifier [0x0x7ff683f28c3e+185118]
-	GetHandleVerifier [0x0x7ff683f3054f+216111]
-	GetHandleVerifier [0x0x7ff683f172e4+113092]
-	GetHandleVerifier [0x0x7ff683f17499+113529]
-	GetHandleVerifier [0x0x7ff683efe298+10616]
+	GetHandleVerifier [0x0x7ff71500e935+77845]
+	GetHandleVerifier [0x0x7ff71500e990+77936]
+	(No symbol) [0x0x7ff714dc9cda]
+	(No symbol) [0x0x7ff714e206aa]
+	(No symbol) [0x0x7ff714e2095c]
+	(No symbol) [0x0x7ff714e73d07]
+	(No symbol) [0x0x7ff714e4890f]
+	(No symbol) [0x0x7ff714e70b07]
+	(No symbol) [0x0x7ff714e486a3]
+	(No symbol) [0x0x7ff714e11791]
+	(No symbol) [0x0x7ff714e12523]
+	GetHandleVerifier [0x0x7ff7152e684d+3059501]
+	GetHandleVerifier [0x0x7ff7152e0c0d+3035885]
+	GetHandleVerifier [0x0x7ff715300400+3164896]
+	GetHandleVerifier [0x0x7ff715028c3e+185118]
+	GetHandleVerifier [0x0x7ff71503054f+216111]
+	GetHandleVerifier [0x0x7ff7150172e4+113092]
+	GetHandleVerifier [0x0x7ff715017499+113529]
+	GetHandleVerifier [0x0x7ff714ffe298+10616]
 	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
 	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
